--- a/_Drive/Publicacoes/mariajose.xlsx
+++ b/_Drive/Publicacoes/mariajose.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="mariajose.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,125 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33" count="33">
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.1016/j.scriptamat.2004.07.026</t>
+  </si>
+  <si>
+    <t>10.1016/j.msea.2017.07.010</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/18/1/006</t>
+  </si>
+  <si>
+    <t>10.1016/j.jmmm.2018.10.034</t>
+  </si>
+  <si>
+    <t>10.1016/j.msea.2015.10.110</t>
+  </si>
+  <si>
+    <t>10.1016/j.msea.2019.04.014</t>
+  </si>
+  <si>
+    <t>10.1016/j.msea.2010.10.051</t>
+  </si>
+  <si>
+    <t>10.1016/j.jnucmat.2015.03.020</t>
+  </si>
+  <si>
+    <t>10.1007/s11661-014-2401-3</t>
+  </si>
+  <si>
+    <t>10.1016/j.jmmm.2016.06.027</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/18/9/001</t>
+  </si>
+  <si>
+    <t>10.1016/j.addma.2019.100979</t>
+  </si>
+  <si>
+    <t>10.1016/j.msea.2019.03.116</t>
+  </si>
+  <si>
+    <t>10.1109/TASC.2005.864287</t>
+  </si>
+  <si>
+    <t>10.1109/TASC.2008.920575</t>
+  </si>
+  <si>
+    <t>10.1016/j.jnucmat.2012.12.017</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/19/12/002</t>
+  </si>
+  <si>
+    <t>10.1016/j.matchar.2016.03.023</t>
+  </si>
+  <si>
+    <t>10.1016/j.jnucmat.2016.12.025</t>
+  </si>
+  <si>
+    <t>10.1088/0953-8984/19/44/446204</t>
+  </si>
+  <si>
+    <t>10.1016/j.actamat.2020.07.038</t>
+  </si>
+  <si>
+    <t>10.1016/j.physc.2006.04.019</t>
+  </si>
+  <si>
+    <t>10.1103/PhysRevB.74.184526</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/19/10/013</t>
+  </si>
+  <si>
+    <t>10.1016/j.scriptamat.2009.10.002</t>
+  </si>
+  <si>
+    <t>10.1051/epjconf/20147504012</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/16/3/301</t>
+  </si>
+  <si>
+    <t>10.1016/j.physc.2004.02.082</t>
+  </si>
+  <si>
+    <t>10.4028/www.scientific.net/MSF.638-642.1995</t>
+  </si>
+  <si>
+    <t>10.1524/zksu.2009.0017</t>
+  </si>
+  <si>
+    <t>10.1016/j.fusengdes.2017.11.003</t>
+  </si>
+  <si>
+    <t>10.1016/j.actamat.2018.12.046</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +176,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,346 +194,288 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="39.28335336538462" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1016/j.scriptamat.2004.07.026</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10.1016/j.msea.2017.07.010</t>
-        </is>
+      <c r="A2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10.1088/0953-2048/18/1/006</t>
-        </is>
+      <c r="A3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10.1016/j.jmmm.2018.10.034</t>
-        </is>
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10.1016/j.phpro.2012.06.122</t>
-        </is>
+      <c r="A5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2015.10.110</t>
+          <t>10.1016/j.phpro.2012.06.122</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10.1016/j.msea.2019.04.014</t>
-        </is>
+      <c r="A7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10.1016/S0921-4534(99)00541-9</t>
-        </is>
+      <c r="A8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.106</t>
+          <t>10.1016/S0921-4534(99)00541-9</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2010.10.051</t>
+          <t>10.1016/j.physc.2004.03.106</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10.1016/j.jnucmat.2015.03.020</t>
-        </is>
+      <c r="A11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10.1007/s11661-014-2401-3</t>
-        </is>
+      <c r="A12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>10.1007/s10948-010-0810-0</t>
-        </is>
+      <c r="A13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1016/j.jmmm.2016.06.027</t>
+          <t>10.1007/s10948-010-0810-0</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10.1088/0953-2048/26/5/055008</t>
-        </is>
+      <c r="A15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/18/9/001</t>
+          <t>10.1088/0953-2048/26/5/055008</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>10.1016/j.addma.2019.100979</t>
-        </is>
+      <c r="A17" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>10.1063/1.345714</t>
-        </is>
+      <c r="A18" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/20/3/028</t>
+          <t>10.1063/1.345714</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1016/S0921-4534(01)00092-2</t>
+          <t>10.1088/0953-2048/20/3/028</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2019.03.116</t>
+          <t>10.1016/S0921-4534(01)00092-2</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10.1590/1980-5373-mr-2016-1107</t>
-        </is>
+      <c r="A22" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2007.04.091</t>
+          <t>10.1590/1980-5373-mr-2016-1107</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2005.864287</t>
+          <t>10.1016/j.physc.2007.04.091</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10.1109/TASC.2002.1018615</t>
-        </is>
+      <c r="A25" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2008.920575</t>
+          <t>10.1109/TASC.2002.1018615</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>10.1016/j.jnucmat.2012.12.017</t>
-        </is>
+      <c r="A27" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>10.1016/j.jmmm2020.167370</t>
-        </is>
+      <c r="A28" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/19/12/002</t>
+          <t>10.1016/j.jmmm2020.167370</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10.1016/j.matchar.2016.03.023</t>
-        </is>
+      <c r="A30" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>10.1016/j.jnucmat.2016.12.025</t>
-        </is>
+      <c r="A31" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>10.1088/0953-8984/19/44/446204</t>
-        </is>
+      <c r="A32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10.1016/j.actamat.2020.07.038</t>
-        </is>
+      <c r="A33" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>10.1016/j.physc.2006.04.019</t>
-        </is>
+      <c r="A34" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>10.1016/S0921-4534(97)01614-6</t>
-        </is>
+      <c r="A35" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevB.74.184526</t>
+          <t>10.1016/S0921-4534(97)01614-6</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>10.1088/0953-2048/19/10/013</t>
-        </is>
+      <c r="A37" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>10.1590/S0103-97332007000700015</t>
-        </is>
+      <c r="A38" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2004.83067</t>
+          <t>10.1590/S0103-97332007000700015</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.1016/j.scriptamat.2009.10.002</t>
+          <t>10.1109/TASC.2004.83067</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>10.1051/epjconf/20147504012</t>
-        </is>
+      <c r="A41" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>10.1088/0953-2048/16/3/301</t>
-        </is>
+      <c r="A42" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>10.1016/j.physc.2004.02.082</t>
-        </is>
+      <c r="A43" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>10.4028/www.scientific.net/MSF.638-642.1995</t>
-        </is>
+      <c r="A44" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>10.1524/zksu.2009.0017</t>
-        </is>
+      <c r="A45" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>10.1016/j.fusengdes.2017.11.003</t>
-        </is>
+      <c r="A46" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>10.1590/S0103-97332007000700014</t>
-        </is>
+      <c r="A47" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.1016/j.actamat.2018.12.046</t>
-        </is>
+          <t>10.1590/S0103-97332007000700014</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
